--- a/diseases/d009/1995-1999.xlsx
+++ b/diseases/d009/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>115</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>105</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>84</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>91</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>100</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>105</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>91</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>41</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>132</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>140</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>142</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>6</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>166</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>6</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>105</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>174</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>158</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>8</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>145</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>7</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>168</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>146</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>4</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>131</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>10</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>148</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>59</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>152</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>3</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>152</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>8</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>144</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>162</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>5</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>109</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>4</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>139</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20645,9 +20498,6 @@
       <c r="O103" t="n">
         <v>4</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21038,9 +20888,6 @@
       <c r="O105" t="n">
         <v>137</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21815,9 +21662,6 @@
       <c r="O109" t="n">
         <v>7</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22208,9 +22052,6 @@
       <c r="O111" t="n">
         <v>152</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22985,9 +22826,6 @@
       <c r="O115" t="n">
         <v>5</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23378,9 +23216,6 @@
       <c r="O117" t="n">
         <v>169</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24155,9 +23990,6 @@
       <c r="O121" t="n">
         <v>6</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24548,9 +24380,6 @@
       <c r="O123" t="n">
         <v>183</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25325,9 +25154,6 @@
       <c r="O127" t="n">
         <v>6</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25718,9 +25544,6 @@
       <c r="O129" t="n">
         <v>140</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26495,9 +26318,6 @@
       <c r="O133" t="n">
         <v>11</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26888,9 +26708,6 @@
       <c r="O135" t="n">
         <v>135</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27665,9 +27482,6 @@
       <c r="O139" t="n">
         <v>91</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28058,9 +27872,6 @@
       <c r="O141" t="n">
         <v>150</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28835,9 +28646,6 @@
       <c r="O145" t="n">
         <v>5</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29228,9 +29036,6 @@
       <c r="O147" t="n">
         <v>190</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30005,9 +29810,6 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30398,9 +30200,6 @@
       <c r="O153" t="n">
         <v>186</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31175,9 +30974,6 @@
       <c r="O157" t="n">
         <v>5</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31568,9 +31364,6 @@
       <c r="O159" t="n">
         <v>134</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32345,9 +32138,6 @@
       <c r="O163" t="n">
         <v>3</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32738,9 +32528,6 @@
       <c r="O165" t="n">
         <v>163</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33515,9 +33302,6 @@
       <c r="O169" t="n">
         <v>12</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33908,9 +33692,6 @@
       <c r="O171" t="n">
         <v>185</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34924,9 +34705,6 @@
       <c r="O176" t="n">
         <v>9</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35317,9 +35095,6 @@
       <c r="O178" t="n">
         <v>175</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36094,9 +35869,6 @@
       <c r="O182" t="n">
         <v>8</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36487,9 +36259,6 @@
       <c r="O184" t="n">
         <v>198</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37264,9 +37033,6 @@
       <c r="O188" t="n">
         <v>8</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37657,9 +37423,6 @@
       <c r="O190" t="n">
         <v>186</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38434,9 +38197,6 @@
       <c r="O194" t="n">
         <v>8</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38827,9 +38587,6 @@
       <c r="O196" t="n">
         <v>161</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39604,9 +39361,6 @@
       <c r="O200" t="n">
         <v>6</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39997,9 +39751,6 @@
       <c r="O202" t="n">
         <v>118</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40774,9 +40525,6 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41167,9 +40915,6 @@
       <c r="O208" t="n">
         <v>148</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41944,9 +41689,6 @@
       <c r="O212" t="n">
         <v>114</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42337,9 +42079,6 @@
       <c r="O214" t="n">
         <v>134</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43114,9 +42853,6 @@
       <c r="O218" t="n">
         <v>5</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43507,9 +43243,6 @@
       <c r="O220" t="n">
         <v>164</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44284,9 +44017,6 @@
       <c r="O224" t="n">
         <v>5</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44677,9 +44407,6 @@
       <c r="O226" t="n">
         <v>147</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45454,9 +45181,6 @@
       <c r="O230" t="n">
         <v>6</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45847,9 +45571,6 @@
       <c r="O232" t="n">
         <v>150</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46624,9 +46345,6 @@
       <c r="O236" t="n">
         <v>14</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47017,9 +46735,6 @@
       <c r="O238" t="n">
         <v>113</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47794,9 +47509,6 @@
       <c r="O242" t="n">
         <v>5</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48187,9 +47899,6 @@
       <c r="O244" t="n">
         <v>107</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49203,9 +48912,6 @@
       <c r="O249" t="n">
         <v>9</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49596,9 +49302,6 @@
       <c r="O251" t="n">
         <v>141</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50373,9 +50076,6 @@
       <c r="O255" t="n">
         <v>11</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="S255" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50766,9 +50466,6 @@
       <c r="O257" t="n">
         <v>177</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51543,9 +51240,6 @@
       <c r="O261" t="n">
         <v>17</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51936,9 +51630,6 @@
       <c r="O263" t="n">
         <v>128</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52713,9 +52404,6 @@
       <c r="O267" t="n">
         <v>9</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53106,9 +52794,6 @@
       <c r="O269" t="n">
         <v>155</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53883,9 +53568,6 @@
       <c r="O273" t="n">
         <v>9</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="S273" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54276,9 +53958,6 @@
       <c r="O275" t="n">
         <v>151</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55053,9 +54732,6 @@
       <c r="O279" t="n">
         <v>8</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55446,9 +55122,6 @@
       <c r="O281" t="n">
         <v>130</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="S281" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56223,9 +55896,6 @@
       <c r="O285" t="n">
         <v>144</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56616,9 +56286,6 @@
       <c r="O287" t="n">
         <v>152</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="S287" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57393,9 +57060,6 @@
       <c r="O291" t="n">
         <v>10</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="S291" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57786,9 +57450,6 @@
       <c r="O293" t="n">
         <v>136</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="S293" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58563,9 +58224,6 @@
       <c r="O297" t="n">
         <v>7</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="S297" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58956,9 +58614,6 @@
       <c r="O299" t="n">
         <v>156</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="S299" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59733,9 +59388,6 @@
       <c r="O303" t="n">
         <v>11</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="S303" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -60126,9 +59778,6 @@
       <c r="O305" t="n">
         <v>181</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="S305" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -60903,9 +60552,6 @@
       <c r="O309" t="n">
         <v>9</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="S309" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61296,9 +60942,6 @@
       <c r="O311" t="n">
         <v>175</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="S311" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -62072,9 +61715,6 @@
       </c>
       <c r="O315" t="n">
         <v>8</v>
-      </c>
-      <c r="Q315" t="n">
-        <v>0</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
